--- a/docs/WBS/作業計画と実績.xlsx
+++ b/docs/WBS/作業計画と実績.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="1" r:id="Rfb80fd17f2964175"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記録根拠" sheetId="2" r:id="R1d283acfc3254521"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="1" r:id="Re3b2c55ce2b14c81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記録根拠" sheetId="2" r:id="R0b6a936738134fc9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -553,7 +553,7 @@
         <x:v>未実施/終了未確認</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="55" customHeight="1">
+    <x:row r="7" ht="92" customHeight="1">
       <x:c r="A7" s="8" t="str">
         <x:v>W-002</x:v>
       </x:c>
@@ -575,17 +575,21 @@
       <x:c r="I7" s="11"/>
       <x:c r="J7" s="14"/>
       <x:c r="K7" s="10" t="str">
-        <x:v>実装担当</x:v>
+        <x:v>確認済みコード記録</x:v>
       </x:c>
       <x:c r="L7" s="10" t="str">
-        <x:v>PR66/68と試験証拠</x:v>
+        <x:v>式場更新API・編集画面／Origin保護</x:v>
       </x:c>
       <x:c r="M7" s="8" t="str">
         <x:v>https://github.com/ryuki-moro/Nicomaru/issues/54</x:v>
       </x:c>
-      <x:c r="N7" s="10"/>
+      <x:c r="N7" s="10" t="str">
+        <x:v>https://github.com/ryuki-moro/Nicomaru/commit/04d9e26</x:v>
+      </x:c>
       <x:c r="O7" s="10"/>
-      <x:c r="P7" s="10"/>
+      <x:c r="P7" s="10" t="str">
+        <x:v>commit記録: 10/8: bd064af,04d9e26／10/9: bc406c4,3f02841。コード記録のみ。本人の作業日・時間・確認者は未確認。</x:v>
+      </x:c>
       <x:c r="Q7" s="8" t="str">
         <x:f>IF(I7="","",I7-F7)</x:f>
       </x:c>
@@ -594,7 +598,7 @@
         <x:v>未実施/終了未確認</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="55" customHeight="1">
+    <x:row r="8" ht="92" customHeight="1">
       <x:c r="A8" s="9" t="str">
         <x:v>W-003</x:v>
       </x:c>
@@ -613,15 +617,13 @@
       </x:c>
       <x:c r="G8" s="10"/>
       <x:c r="H8" s="11"/>
-      <x:c r="I8" s="11" t="d">
-        <x:v>2026-10-09T00:00:00.000Z</x:v>
-      </x:c>
+      <x:c r="I8" s="11"/>
       <x:c r="J8" s="14"/>
       <x:c r="K8" s="10" t="str">
         <x:v>確認済みコード記録</x:v>
       </x:c>
       <x:c r="L8" s="10" t="str">
-        <x:v>66cdede</x:v>
+        <x:v>削除バッチの部分失敗・再試行・二重集計修正</x:v>
       </x:c>
       <x:c r="M8" s="9" t="str">
         <x:v>https://github.com/ryuki-moro/Nicomaru/issues/69</x:v>
@@ -630,17 +632,18 @@
         <x:v>https://github.com/ryuki-moro/Nicomaru/commit/66cdede</x:v>
       </x:c>
       <x:c r="O8" s="10"/>
-      <x:c r="P8" s="10"/>
-      <x:c r="Q8" s="9" t="n">
+      <x:c r="P8" s="10" t="str">
+        <x:v>commit記録: 10/9: 66cdede,579d7d9。旧終了日10/9はcommit日。本人の終了日と区別し実績終了を空欄に変更。</x:v>
+      </x:c>
+      <x:c r="Q8" s="9" t="str">
         <x:f>IF(I8="","",I8-F8)</x:f>
-        <x:v>-22</x:v>
       </x:c>
       <x:c r="R8" s="9" t="str">
         <x:f>IF(I8="","未実施/終了未確認",IF(OR(G8="",N8="",O8=""),"担当・証拠・確認者を記入","確認欄あり"))</x:f>
-        <x:v>担当・証拠・確認者を記入</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="55" customHeight="1">
+        <x:v>未実施/終了未確認</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="92" customHeight="1">
       <x:c r="A9" s="8" t="str">
         <x:v>W-004</x:v>
       </x:c>
@@ -659,15 +662,13 @@
       </x:c>
       <x:c r="G9" s="10"/>
       <x:c r="H9" s="11"/>
-      <x:c r="I9" s="11" t="d">
-        <x:v>2026-10-09T00:00:00.000Z</x:v>
-      </x:c>
+      <x:c r="I9" s="11"/>
       <x:c r="J9" s="14"/>
       <x:c r="K9" s="10" t="str">
         <x:v>確認済みコード記録</x:v>
       </x:c>
       <x:c r="L9" s="10" t="str">
-        <x:v>99c1e6f</x:v>
+        <x:v>Next.js・sharp等の依存修正</x:v>
       </x:c>
       <x:c r="M9" s="8" t="str">
         <x:v>https://github.com/ryuki-moro/Nicomaru/issues/47</x:v>
@@ -676,17 +677,18 @@
         <x:v>https://github.com/ryuki-moro/Nicomaru/commit/99c1e6f</x:v>
       </x:c>
       <x:c r="O9" s="10"/>
-      <x:c r="P9" s="10"/>
-      <x:c r="Q9" s="8" t="n">
+      <x:c r="P9" s="10" t="str">
+        <x:v>commit記録: 10/6: 0a8fe5b,d8f8ce2／10/9: 99c1e6f。旧終了日10/9はcommit日。本人の終了日と区別し実績終了を空欄に変更。</x:v>
+      </x:c>
+      <x:c r="Q9" s="8" t="str">
         <x:f>IF(I9="","",I9-F9)</x:f>
-        <x:v>-22</x:v>
       </x:c>
       <x:c r="R9" s="8" t="str">
         <x:f>IF(I9="","未実施/終了未確認",IF(OR(G9="",N9="",O9=""),"担当・証拠・確認者を記入","確認欄あり"))</x:f>
-        <x:v>担当・証拠・確認者を記入</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="55" customHeight="1">
+        <x:v>未実施/終了未確認</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="92" customHeight="1">
       <x:c r="A10" s="9" t="str">
         <x:v>W-005</x:v>
       </x:c>
@@ -708,17 +710,21 @@
       <x:c r="I10" s="11"/>
       <x:c r="J10" s="14"/>
       <x:c r="K10" s="10" t="str">
-        <x:v>実装担当</x:v>
+        <x:v>確認済みコード記録</x:v>
       </x:c>
       <x:c r="L10" s="10" t="str">
-        <x:v>今回の実装差分/CI</x:v>
+        <x:v>監視・監査イベント保護・監査待機の修正</x:v>
       </x:c>
       <x:c r="M10" s="9" t="str">
         <x:v>https://github.com/ryuki-moro/Nicomaru/issues/54</x:v>
       </x:c>
-      <x:c r="N10" s="10"/>
+      <x:c r="N10" s="10" t="str">
+        <x:v>https://github.com/ryuki-moro/Nicomaru/commit/cf739a9</x:v>
+      </x:c>
       <x:c r="O10" s="10"/>
-      <x:c r="P10" s="10"/>
+      <x:c r="P10" s="10" t="str">
+        <x:v>commit記録: 10/9: cf739a9,15d2367,ad96179。コード記録のみ。容量集計等を含む行全体の完了や人の試験実施は未確認。</x:v>
+      </x:c>
       <x:c r="Q10" s="9" t="str">
         <x:f>IF(I10="","",I10-F10)</x:f>
       </x:c>
@@ -727,7 +733,7 @@
         <x:v>未実施/終了未確認</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="55" customHeight="1">
+    <x:row r="11" ht="92" customHeight="1">
       <x:c r="A11" s="8" t="str">
         <x:v>W-006</x:v>
       </x:c>
@@ -749,17 +755,21 @@
       <x:c r="I11" s="11"/>
       <x:c r="J11" s="14"/>
       <x:c r="K11" s="10" t="str">
-        <x:v>実装担当</x:v>
+        <x:v>確認済みコード記録</x:v>
       </x:c>
       <x:c r="L11" s="10" t="str">
-        <x:v>今回の実装差分/CI</x:v>
+        <x:v>PWA・性能検証準備・依存更新自動化・整形</x:v>
       </x:c>
       <x:c r="M11" s="8" t="str">
         <x:v>https://github.com/ryuki-moro/Nicomaru/issues/54</x:v>
       </x:c>
-      <x:c r="N11" s="10"/>
+      <x:c r="N11" s="10" t="str">
+        <x:v>https://github.com/ryuki-moro/Nicomaru/commit/cf739a9</x:v>
+      </x:c>
       <x:c r="O11" s="10"/>
-      <x:c r="P11" s="10"/>
+      <x:c r="P11" s="10" t="str">
+        <x:v>commit記録: 10/9: cf739a9,9d6a696,c6048b2。コード記録のみ。実端末試験・本人実績は未確認。</x:v>
+      </x:c>
       <x:c r="Q11" s="8" t="str">
         <x:f>IF(I11="","",I11-F11)</x:f>
       </x:c>
@@ -768,7 +778,7 @@
         <x:v>未実施/終了未確認</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="55" customHeight="1">
+    <x:row r="12" ht="92" customHeight="1">
       <x:c r="A12" s="9" t="str">
         <x:v>W-007</x:v>
       </x:c>
@@ -790,17 +800,21 @@
       <x:c r="I12" s="11"/>
       <x:c r="J12" s="14"/>
       <x:c r="K12" s="10" t="str">
-        <x:v>メンバー確認</x:v>
+        <x:v>確認済みコード記録</x:v>
       </x:c>
       <x:c r="L12" s="10" t="str">
-        <x:v>詳細設計図</x:v>
+        <x:v>docs/詳細設計/詳細設計図.pdf ほか</x:v>
       </x:c>
       <x:c r="M12" s="9" t="str">
         <x:v>https://github.com/ryuki-moro/Nicomaru/issues/50</x:v>
       </x:c>
-      <x:c r="N12" s="10"/>
+      <x:c r="N12" s="10" t="str">
+        <x:v>https://github.com/ryuki-moro/Nicomaru/commit/832bc81</x:v>
+      </x:c>
       <x:c r="O12" s="10"/>
-      <x:c r="P12" s="10"/>
+      <x:c r="P12" s="10" t="str">
+        <x:v>commit記録: 10/9: 832bc81。資料の作成記録。別メンバーによるコード照合・確認は未確認。</x:v>
+      </x:c>
       <x:c r="Q12" s="9" t="str">
         <x:f>IF(I12="","",I12-F12)</x:f>
       </x:c>
@@ -809,7 +823,7 @@
         <x:v>未実施/終了未確認</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="55" customHeight="1">
+    <x:row r="13" ht="92" customHeight="1">
       <x:c r="A13" s="8" t="str">
         <x:v>W-008</x:v>
       </x:c>
@@ -831,17 +845,21 @@
       <x:c r="I13" s="11"/>
       <x:c r="J13" s="14"/>
       <x:c r="K13" s="10" t="str">
-        <x:v>メンバー確認</x:v>
+        <x:v>確認済みコード記録</x:v>
       </x:c>
       <x:c r="L13" s="10" t="str">
-        <x:v>PowerPoint/原稿</x:v>
+        <x:v>docs/発表/中間発表/ のPowerPoint・原稿</x:v>
       </x:c>
       <x:c r="M13" s="8" t="str">
         <x:v>https://github.com/ryuki-moro/Nicomaru/issues/51</x:v>
       </x:c>
-      <x:c r="N13" s="10"/>
+      <x:c r="N13" s="10" t="str">
+        <x:v>https://github.com/ryuki-moro/Nicomaru/commit/832bc81</x:v>
+      </x:c>
       <x:c r="O13" s="10"/>
-      <x:c r="P13" s="10"/>
+      <x:c r="P13" s="10" t="str">
+        <x:v>commit記録: 10/9: 832bc81。雛形の作成記録。本人の編集日・時間や発表実施は未確認。</x:v>
+      </x:c>
       <x:c r="Q13" s="8" t="str">
         <x:f>IF(I13="","",I13-F13)</x:f>
       </x:c>
@@ -891,7 +909,7 @@
         <x:v>未実施/終了未確認</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="55" customHeight="1">
+    <x:row r="15" ht="92" customHeight="1">
       <x:c r="A15" s="8" t="str">
         <x:v>W-010</x:v>
       </x:c>
@@ -913,17 +931,21 @@
       <x:c r="I15" s="11"/>
       <x:c r="J15" s="14"/>
       <x:c r="K15" s="10" t="str">
-        <x:v>本人入力</x:v>
+        <x:v>確認済みコード記録</x:v>
       </x:c>
       <x:c r="L15" s="10" t="str">
-        <x:v>本ブックの実績欄</x:v>
+        <x:v>docs/WBS/作業計画と実績.xlsx</x:v>
       </x:c>
       <x:c r="M15" s="8" t="str">
         <x:v>https://github.com/ryuki-moro/Nicomaru/issues/65</x:v>
       </x:c>
-      <x:c r="N15" s="10"/>
+      <x:c r="N15" s="10" t="str">
+        <x:v>https://github.com/ryuki-moro/Nicomaru/commit/832bc81</x:v>
+      </x:c>
       <x:c r="O15" s="10"/>
-      <x:c r="P15" s="10"/>
+      <x:c r="P15" s="10" t="str">
+        <x:v>commit記録: 10/9: 832bc81。WBSの雛形作成記録。今回の証拠追記と本人の作業時間の確認は別。</x:v>
+      </x:c>
       <x:c r="Q15" s="8" t="str">
         <x:f>IF(I15="","",I15-F15)</x:f>
       </x:c>
@@ -1793,39 +1815,112 @@
         <x:v>未実施/終了未確認</x:v>
       </x:c>
     </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="1"/>
-      <x:c r="B37" s="1"/>
-      <x:c r="C37" s="1"/>
-      <x:c r="D37" s="1"/>
-      <x:c r="E37" s="1"/>
-      <x:c r="F37" s="1"/>
-      <x:c r="G37" s="1"/>
-      <x:c r="H37" s="1"/>
-      <x:c r="I37" s="1"/>
-      <x:c r="J37" s="1"/>
-      <x:c r="K37" s="1"/>
-      <x:c r="L37" s="1"/>
-      <x:c r="M37" s="1"/>
-      <x:c r="N37" s="1"/>
-      <x:c r="O37" s="1"/>
-      <x:c r="P37" s="1"/>
-      <x:c r="Q37" s="1"/>
-      <x:c r="R37" s="1"/>
+    <x:row r="37" ht="92" customHeight="1">
+      <x:c r="A37" s="8" t="str">
+        <x:v>W-032</x:v>
+      </x:c>
+      <x:c r="B37" s="8" t="str">
+        <x:v>10月</x:v>
+      </x:c>
+      <x:c r="C37" s="8" t="str">
+        <x:v>実装</x:v>
+      </x:c>
+      <x:c r="D37" s="8" t="str">
+        <x:v>通知CSVの期間指定・ページング・画面対応</x:v>
+      </x:c>
+      <x:c r="E37" s="11"/>
+      <x:c r="F37" s="13" t="d">
+        <x:v>2026-10-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G37" s="10"/>
+      <x:c r="H37" s="11"/>
+      <x:c r="I37" s="11"/>
+      <x:c r="J37" s="14"/>
+      <x:c r="K37" s="10" t="str">
+        <x:v>確認済みコード記録</x:v>
+      </x:c>
+      <x:c r="L37" s="10" t="str">
+        <x:v>通知CSV API・入力フォーム・回帰テスト</x:v>
+      </x:c>
+      <x:c r="M37" s="8" t="str">
+        <x:v>https://github.com/ryuki-moro/Nicomaru/issues/116</x:v>
+      </x:c>
+      <x:c r="N37" s="10" t="str">
+        <x:v>https://github.com/ryuki-moro/Nicomaru/commit/e8991d6</x:v>
+      </x:c>
+      <x:c r="O37" s="10"/>
+      <x:c r="P37" s="10" t="str">
+        <x:v>commit記録: 10/6: e8991d6,2fbe2ed,1cfb7d9。本人の実績日・時間・確認者は未確認。</x:v>
+      </x:c>
+      <x:c r="Q37" s="8" t="str">
+        <x:f>IF(I37="","",I37-F37)</x:f>
+      </x:c>
+      <x:c r="R37" s="8" t="str">
+        <x:f>IF(I37="","未実施/終了未確認",IF(OR(G37="",N37="",O37=""),"担当・証拠・確認者を記入","確認者と照合"))</x:f>
+        <x:v>未実施/終了未確認</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="92" customHeight="1">
+      <x:c r="A38" s="8" t="str">
+        <x:v>W-033</x:v>
+      </x:c>
+      <x:c r="B38" s="8" t="str">
+        <x:v>10月</x:v>
+      </x:c>
+      <x:c r="C38" s="8" t="str">
+        <x:v>実装</x:v>
+      </x:c>
+      <x:c r="D38" s="8" t="str">
+        <x:v>式場プレビュー認証・接続タイムアウトを修正</x:v>
+      </x:c>
+      <x:c r="E38" s="11"/>
+      <x:c r="F38" s="13" t="d">
+        <x:v>2026-10-31T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G38" s="10"/>
+      <x:c r="H38" s="11"/>
+      <x:c r="I38" s="11"/>
+      <x:c r="J38" s="14"/>
+      <x:c r="K38" s="10" t="str">
+        <x:v>確認済みコード記録</x:v>
+      </x:c>
+      <x:c r="L38" s="10" t="str">
+        <x:v>プレビュー認証と接続タイムアウト修正</x:v>
+      </x:c>
+      <x:c r="M38" s="8" t="str">
+        <x:v>https://github.com/ryuki-moro/Nicomaru/issues/116</x:v>
+      </x:c>
+      <x:c r="N38" s="10" t="str">
+        <x:v>https://github.com/ryuki-moro/Nicomaru/commit/ae62a53</x:v>
+      </x:c>
+      <x:c r="O38" s="10"/>
+      <x:c r="P38" s="10" t="str">
+        <x:v>commit記録: 10/8: ae62a53,6076dd0。本人の実績日・時間・確認者は未確認。</x:v>
+      </x:c>
+      <x:c r="Q38" s="8" t="str">
+        <x:f>IF(I38="","",I38-F38)</x:f>
+      </x:c>
+      <x:c r="R38" s="8" t="str">
+        <x:f>IF(I38="","未実施/終了未確認",IF(OR(G38="",N38="",O38=""),"担当・証拠・確認者を記入","確認者と照合"))</x:f>
+        <x:v>未実施/終了未確認</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A2:F2"/>
     <x:mergeCell ref="A3:F3"/>
   </x:mergeCells>
-  <x:dataValidations count="1">
+  <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="K6:K36">
+      <x:formula1>"将来予定,人間未実施,本人入力,実装担当,メンバー確認,チーム確認,確認済みコード記録,進行中,完了,保留,中止"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="K37:K38">
       <x:formula1>"将来予定,人間未実施,本人入力,実装担当,メンバー確認,チーム確認,確認済みコード記録,進行中,完了,保留,中止"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R525e7b2b85914ba5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9631e178b3a24da3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1938,7 +2033,7 @@
         <x:v>https://github.com/ryuki-moro/Nicomaru</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="34" customHeight="1">
+    <x:row r="10" ht="64" customHeight="1">
       <x:c r="A10" s="9" t="str">
         <x:v>確認済み出来事</x:v>
       </x:c>
@@ -1946,13 +2041,13 @@
         <x:v>66cdede / 2026-10-09</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
-        <x:v>削除バッチ修正がコミットされたことのみ確認。担当者の作業時間は未確認</x:v>
+        <x:v>10/9はcommit作成日。本人実績日は未確認のためWBS実績終了欄は空欄。</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
         <x:v>https://github.com/ryuki-moro/Nicomaru/commit/66cdede</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="34" customHeight="1">
+    <x:row r="11" ht="64" customHeight="1">
       <x:c r="A11" s="8" t="str">
         <x:v>確認済み出来事</x:v>
       </x:c>
@@ -1960,7 +2055,7 @@
         <x:v>99c1e6f / 2026-10-09</x:v>
       </x:c>
       <x:c r="C11" s="8" t="str">
-        <x:v>依存更新がコミットされたことのみ確認。担当者の作業時間は未確認</x:v>
+        <x:v>10/9はcommit作成日。本人実績日は未確認のためWBS実績終了欄は空欄。</x:v>
       </x:c>
       <x:c r="D11" s="8" t="str">
         <x:v>https://github.com/ryuki-moro/Nicomaru/commit/99c1e6f</x:v>
@@ -1993,7 +2088,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re92ba0c1b1bb4bcb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd943c18c18584004"/>
   </x:tableParts>
 </x:worksheet>
 </file>